--- a/storage/testing/payable-tax-import.xlsx
+++ b/storage/testing/payable-tax-import.xlsx
@@ -56,7 +56,7 @@
     <t>PRJ-001</t>
   </si>
   <si>
-    <t>AKN-0215</t>
+    <t>AKN-6547</t>
   </si>
   <si>
     <t>VENDOR</t>
